--- a/data/processed/positivacao/2023-10_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-10_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25933,7 +25933,7 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B985" t="inlineStr"/>
@@ -37155,7 +37155,7 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr"/>
@@ -65969,7 +65969,7 @@
     <row r="2526">
       <c r="A2526" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2526" t="inlineStr"/>
@@ -67666,12 +67666,12 @@
       <c r="A2592" t="inlineStr"/>
       <c r="B2592" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 3 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 2.593,59
+          <t>Vendedor 1 - VENDEDOR 01: positivou 3 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 2.593,59
 Vendedor 18 - LOJA: positivou 180 cliente(s), não positivou 709 cliente(s) - Total vendido: R$ 75.810,54
-Vendedor 3 - FERNANDA: positivou 110 cliente(s), não positivou 321 cliente(s) - Total vendido: R$ 143.107,30
-Vendedor 4 - DANIELA: positivou 96 cliente(s), não positivou 566 cliente(s) - Total vendido: R$ 54.821,08
+Vendedor 3 - VENDEDOR 03: positivou 110 cliente(s), não positivou 321 cliente(s) - Total vendido: R$ 143.107,30
+Vendedor 4 - VENDEDOR 04: positivou 96 cliente(s), não positivou 566 cliente(s) - Total vendido: R$ 54.821,08
 Vendedor 5 - SITE: positivou 8 cliente(s), não positivou 437 cliente(s) - Total vendido: R$ 1.693,61
-Vendedor 8 - RAFAEL: positivou 1 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 133,80</t>
+Vendedor 8 - VENDEDOR 08: positivou 1 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 133,80</t>
         </is>
       </c>
       <c r="C2592" t="inlineStr"/>
